--- a/Assets/Config/Holmas_PlayerLevelTable.xlsx
+++ b/Assets/Config/Holmas_PlayerLevelTable.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Holmas\Assets\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C41263A1-D0F4-4DB8-8A20-D5306FE124C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1422C470-D583-4E08-8C3D-BC490DD399B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Holmas_PlayerLevelTable" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="65">
   <si>
     <t>玩家等级</t>
   </si>
@@ -202,12 +202,30 @@
   </si>
   <si>
     <t>5;20;75</t>
+  </si>
+  <si>
+    <t>达到该等级所需累计经验</t>
+  </si>
+  <si>
+    <t>每小时离线奖励</t>
+  </si>
+  <si>
+    <t>广告解锁时长</t>
+  </si>
+  <si>
+    <t>minExperience</t>
+  </si>
+  <si>
+    <t>offlineRewardPerHour</t>
+  </si>
+  <si>
+    <t>adUnlockHours</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1152,381 +1170,2659 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+      <c r="D3">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1440</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>1680</v>
+      </c>
+      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>36</v>
+      </c>
+      <c r="C6">
+        <v>1920</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>51</v>
+      </c>
+      <c r="C7">
+        <v>2160</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>66</v>
+      </c>
+      <c r="C8">
+        <v>4200</v>
+      </c>
+      <c r="D8">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>81</v>
+      </c>
+      <c r="C9">
+        <v>4560</v>
+      </c>
+      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>96</v>
+      </c>
+      <c r="C10">
+        <v>4920</v>
+      </c>
+      <c r="D10">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>111</v>
+      </c>
+      <c r="C11">
+        <v>5280</v>
+      </c>
+      <c r="D11">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>126</v>
+      </c>
+      <c r="C12">
+        <v>5640</v>
+      </c>
+      <c r="D12">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>141</v>
+      </c>
+      <c r="C13">
+        <v>6000</v>
+      </c>
+      <c r="D13">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>156</v>
+      </c>
+      <c r="C14">
+        <v>6360</v>
+      </c>
+      <c r="D14">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>171</v>
+      </c>
+      <c r="C15">
+        <v>6720</v>
+      </c>
+      <c r="D15">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>44</v>
       </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>186</v>
+      </c>
+      <c r="C16">
+        <v>7080</v>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>46</v>
       </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>201</v>
+      </c>
+      <c r="C17">
+        <v>7440</v>
+      </c>
+      <c r="D17">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>20</v>
       </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>216</v>
+      </c>
+      <c r="C18">
+        <v>7800</v>
+      </c>
+      <c r="D18">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>50</v>
       </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>231</v>
+      </c>
+      <c r="C19">
+        <v>8160</v>
+      </c>
+      <c r="D19">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
         <v>52</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>32</v>
       </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>246</v>
+      </c>
+      <c r="C20">
+        <v>8520</v>
+      </c>
+      <c r="D20">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
         <v>35</v>
       </c>
-      <c r="D20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>261</v>
+      </c>
+      <c r="C21">
+        <v>8880</v>
+      </c>
+      <c r="D21">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
         <v>56</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
         <v>29</v>
       </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" t="s">
-        <v>21</v>
+      <c r="B22">
+        <v>276</v>
+      </c>
+      <c r="C22">
+        <v>9240</v>
+      </c>
+      <c r="D22">
+        <v>24</v>
       </c>
       <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>291</v>
+      </c>
+      <c r="C23">
+        <v>15000</v>
+      </c>
+      <c r="D23">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>306</v>
+      </c>
+      <c r="C24">
+        <v>15360</v>
+      </c>
+      <c r="D24">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>321</v>
+      </c>
+      <c r="C25">
+        <v>15720</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>336</v>
+      </c>
+      <c r="C26">
+        <v>16080</v>
+      </c>
+      <c r="D26">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>351</v>
+      </c>
+      <c r="C27">
+        <v>16440</v>
+      </c>
+      <c r="D27">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>366</v>
+      </c>
+      <c r="C28">
+        <v>16800</v>
+      </c>
+      <c r="D28">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>381</v>
+      </c>
+      <c r="C29">
+        <v>17160</v>
+      </c>
+      <c r="D29">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>396</v>
+      </c>
+      <c r="C30">
+        <v>17520</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>411</v>
+      </c>
+      <c r="C31">
+        <v>17880</v>
+      </c>
+      <c r="D31">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>426</v>
+      </c>
+      <c r="C32">
+        <v>18240</v>
+      </c>
+      <c r="D32">
+        <v>24</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>441</v>
+      </c>
+      <c r="C33">
+        <v>18600</v>
+      </c>
+      <c r="D33">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>456</v>
+      </c>
+      <c r="C34">
+        <v>18960</v>
+      </c>
+      <c r="D34">
+        <v>24</v>
+      </c>
+      <c r="E34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>471</v>
+      </c>
+      <c r="C35">
+        <v>19320</v>
+      </c>
+      <c r="D35">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G35" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>486</v>
+      </c>
+      <c r="C36">
+        <v>19680</v>
+      </c>
+      <c r="D36">
+        <v>24</v>
+      </c>
+      <c r="E36" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>501</v>
+      </c>
+      <c r="C37">
+        <v>20040</v>
+      </c>
+      <c r="D37">
+        <v>24</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>516</v>
+      </c>
+      <c r="C38">
+        <v>20400</v>
+      </c>
+      <c r="D38">
+        <v>24</v>
+      </c>
+      <c r="E38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>531</v>
+      </c>
+      <c r="C39">
+        <v>20760</v>
+      </c>
+      <c r="D39">
+        <v>24</v>
+      </c>
+      <c r="E39" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>546</v>
+      </c>
+      <c r="C40">
+        <v>21120</v>
+      </c>
+      <c r="D40">
+        <v>24</v>
+      </c>
+      <c r="E40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>561</v>
+      </c>
+      <c r="C41">
+        <v>21480</v>
+      </c>
+      <c r="D41">
+        <v>24</v>
+      </c>
+      <c r="E41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>576</v>
+      </c>
+      <c r="C42">
+        <v>21840</v>
+      </c>
+      <c r="D42">
+        <v>24</v>
+      </c>
+      <c r="E42" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>591</v>
+      </c>
+      <c r="C43">
+        <v>41400</v>
+      </c>
+      <c r="D43">
+        <v>24</v>
+      </c>
+      <c r="E43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>606</v>
+      </c>
+      <c r="C44">
+        <v>42000</v>
+      </c>
+      <c r="D44">
+        <v>24</v>
+      </c>
+      <c r="E44" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>621</v>
+      </c>
+      <c r="C45">
+        <v>42600</v>
+      </c>
+      <c r="D45">
+        <v>24</v>
+      </c>
+      <c r="E45" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>636</v>
+      </c>
+      <c r="C46">
+        <v>43200</v>
+      </c>
+      <c r="D46">
+        <v>24</v>
+      </c>
+      <c r="E46" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>651</v>
+      </c>
+      <c r="C47">
+        <v>43800</v>
+      </c>
+      <c r="D47">
+        <v>24</v>
+      </c>
+      <c r="E47" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" t="s">
+        <v>41</v>
+      </c>
+      <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>666</v>
+      </c>
+      <c r="C48">
+        <v>44400</v>
+      </c>
+      <c r="D48">
+        <v>24</v>
+      </c>
+      <c r="E48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>681</v>
+      </c>
+      <c r="C49">
+        <v>45000</v>
+      </c>
+      <c r="D49">
+        <v>24</v>
+      </c>
+      <c r="E49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>696</v>
+      </c>
+      <c r="C50">
+        <v>45600</v>
+      </c>
+      <c r="D50">
+        <v>24</v>
+      </c>
+      <c r="E50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>711</v>
+      </c>
+      <c r="C51">
+        <v>46200</v>
+      </c>
+      <c r="D51">
+        <v>24</v>
+      </c>
+      <c r="E51" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>726</v>
+      </c>
+      <c r="C52">
+        <v>46800</v>
+      </c>
+      <c r="D52">
+        <v>24</v>
+      </c>
+      <c r="E52" t="s">
+        <v>54</v>
+      </c>
+      <c r="F52" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>741</v>
+      </c>
+      <c r="C53">
+        <v>47400</v>
+      </c>
+      <c r="D53">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
+        <v>54</v>
+      </c>
+      <c r="F53" t="s">
+        <v>41</v>
+      </c>
+      <c r="G53" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>756</v>
+      </c>
+      <c r="C54">
+        <v>48000</v>
+      </c>
+      <c r="D54">
+        <v>24</v>
+      </c>
+      <c r="E54" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>771</v>
+      </c>
+      <c r="C55">
+        <v>48600</v>
+      </c>
+      <c r="D55">
+        <v>24</v>
+      </c>
+      <c r="E55" t="s">
+        <v>54</v>
+      </c>
+      <c r="F55" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>786</v>
+      </c>
+      <c r="C56">
+        <v>49200</v>
+      </c>
+      <c r="D56">
+        <v>24</v>
+      </c>
+      <c r="E56" t="s">
+        <v>54</v>
+      </c>
+      <c r="F56" t="s">
+        <v>41</v>
+      </c>
+      <c r="G56" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>801</v>
+      </c>
+      <c r="C57">
+        <v>49800</v>
+      </c>
+      <c r="D57">
+        <v>24</v>
+      </c>
+      <c r="E57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>816</v>
+      </c>
+      <c r="C58">
+        <v>50400</v>
+      </c>
+      <c r="D58">
+        <v>24</v>
+      </c>
+      <c r="E58" t="s">
+        <v>54</v>
+      </c>
+      <c r="F58" t="s">
+        <v>41</v>
+      </c>
+      <c r="G58" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>831</v>
+      </c>
+      <c r="C59">
+        <v>51000</v>
+      </c>
+      <c r="D59">
+        <v>24</v>
+      </c>
+      <c r="E59" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>846</v>
+      </c>
+      <c r="C60">
+        <v>51600</v>
+      </c>
+      <c r="D60">
+        <v>24</v>
+      </c>
+      <c r="E60" t="s">
+        <v>54</v>
+      </c>
+      <c r="F60" t="s">
+        <v>41</v>
+      </c>
+      <c r="G60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>861</v>
+      </c>
+      <c r="C61">
+        <v>52200</v>
+      </c>
+      <c r="D61">
+        <v>24</v>
+      </c>
+      <c r="E61" t="s">
+        <v>54</v>
+      </c>
+      <c r="F61" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>876</v>
+      </c>
+      <c r="C62">
+        <v>52800</v>
+      </c>
+      <c r="D62">
+        <v>24</v>
+      </c>
+      <c r="E62" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>891</v>
+      </c>
+      <c r="C63">
+        <v>72600</v>
+      </c>
+      <c r="D63">
+        <v>24</v>
+      </c>
+      <c r="E63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>906</v>
+      </c>
+      <c r="C64">
+        <v>73320</v>
+      </c>
+      <c r="D64">
+        <v>24</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" t="s">
+        <v>41</v>
+      </c>
+      <c r="G64" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>921</v>
+      </c>
+      <c r="C65">
+        <v>74040</v>
+      </c>
+      <c r="D65">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
+        <v>54</v>
+      </c>
+      <c r="F65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G65" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>936</v>
+      </c>
+      <c r="C66">
+        <v>74760</v>
+      </c>
+      <c r="D66">
+        <v>24</v>
+      </c>
+      <c r="E66" t="s">
+        <v>54</v>
+      </c>
+      <c r="F66" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>951</v>
+      </c>
+      <c r="C67">
+        <v>75480</v>
+      </c>
+      <c r="D67">
+        <v>24</v>
+      </c>
+      <c r="E67" t="s">
+        <v>54</v>
+      </c>
+      <c r="F67" t="s">
+        <v>41</v>
+      </c>
+      <c r="G67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>966</v>
+      </c>
+      <c r="C68">
+        <v>76200</v>
+      </c>
+      <c r="D68">
+        <v>24</v>
+      </c>
+      <c r="E68" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" t="s">
+        <v>41</v>
+      </c>
+      <c r="G68" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>981</v>
+      </c>
+      <c r="C69">
+        <v>76920</v>
+      </c>
+      <c r="D69">
+        <v>24</v>
+      </c>
+      <c r="E69" t="s">
+        <v>54</v>
+      </c>
+      <c r="F69" t="s">
+        <v>41</v>
+      </c>
+      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>996</v>
+      </c>
+      <c r="C70">
+        <v>77640</v>
+      </c>
+      <c r="D70">
+        <v>24</v>
+      </c>
+      <c r="E70" t="s">
+        <v>54</v>
+      </c>
+      <c r="F70" t="s">
+        <v>41</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>1011</v>
+      </c>
+      <c r="C71">
+        <v>78360</v>
+      </c>
+      <c r="D71">
+        <v>24</v>
+      </c>
+      <c r="E71" t="s">
+        <v>54</v>
+      </c>
+      <c r="F71" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" t="s">
+        <v>21</v>
+      </c>
+      <c r="H71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>1026</v>
+      </c>
+      <c r="C72">
+        <v>79080</v>
+      </c>
+      <c r="D72">
+        <v>24</v>
+      </c>
+      <c r="E72" t="s">
+        <v>54</v>
+      </c>
+      <c r="F72" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>1041</v>
+      </c>
+      <c r="C73">
+        <v>79800</v>
+      </c>
+      <c r="D73">
+        <v>24</v>
+      </c>
+      <c r="E73" t="s">
+        <v>54</v>
+      </c>
+      <c r="F73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G73" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>1056</v>
+      </c>
+      <c r="C74">
+        <v>80520</v>
+      </c>
+      <c r="D74">
+        <v>24</v>
+      </c>
+      <c r="E74" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>1071</v>
+      </c>
+      <c r="C75">
+        <v>81240</v>
+      </c>
+      <c r="D75">
+        <v>24</v>
+      </c>
+      <c r="E75" t="s">
+        <v>54</v>
+      </c>
+      <c r="F75" t="s">
+        <v>41</v>
+      </c>
+      <c r="G75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>1086</v>
+      </c>
+      <c r="C76">
+        <v>81960</v>
+      </c>
+      <c r="D76">
+        <v>24</v>
+      </c>
+      <c r="E76" t="s">
+        <v>54</v>
+      </c>
+      <c r="F76" t="s">
+        <v>41</v>
+      </c>
+      <c r="G76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>1101</v>
+      </c>
+      <c r="C77">
+        <v>82680</v>
+      </c>
+      <c r="D77">
+        <v>24</v>
+      </c>
+      <c r="E77" t="s">
+        <v>54</v>
+      </c>
+      <c r="F77" t="s">
+        <v>41</v>
+      </c>
+      <c r="G77" t="s">
+        <v>21</v>
+      </c>
+      <c r="H77" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>1116</v>
+      </c>
+      <c r="C78">
+        <v>83400</v>
+      </c>
+      <c r="D78">
+        <v>24</v>
+      </c>
+      <c r="E78" t="s">
+        <v>54</v>
+      </c>
+      <c r="F78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>1131</v>
+      </c>
+      <c r="C79">
+        <v>84120</v>
+      </c>
+      <c r="D79">
+        <v>24</v>
+      </c>
+      <c r="E79" t="s">
+        <v>54</v>
+      </c>
+      <c r="F79" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" t="s">
+        <v>21</v>
+      </c>
+      <c r="H79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>1146</v>
+      </c>
+      <c r="C80">
+        <v>84840</v>
+      </c>
+      <c r="D80">
+        <v>24</v>
+      </c>
+      <c r="E80" t="s">
+        <v>54</v>
+      </c>
+      <c r="F80" t="s">
+        <v>41</v>
+      </c>
+      <c r="G80" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>1161</v>
+      </c>
+      <c r="C81">
+        <v>85560</v>
+      </c>
+      <c r="D81">
+        <v>24</v>
+      </c>
+      <c r="E81" t="s">
+        <v>54</v>
+      </c>
+      <c r="F81" t="s">
+        <v>41</v>
+      </c>
+      <c r="G81" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>1176</v>
+      </c>
+      <c r="C82">
+        <v>86280</v>
+      </c>
+      <c r="D82">
+        <v>24</v>
+      </c>
+      <c r="E82" t="s">
+        <v>54</v>
+      </c>
+      <c r="F82" t="s">
+        <v>41</v>
+      </c>
+      <c r="G82" t="s">
+        <v>21</v>
+      </c>
+      <c r="H82" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>1191</v>
+      </c>
+      <c r="C83">
+        <v>87000</v>
+      </c>
+      <c r="D83">
+        <v>24</v>
+      </c>
+      <c r="E83" t="s">
+        <v>54</v>
+      </c>
+      <c r="F83" t="s">
+        <v>41</v>
+      </c>
+      <c r="G83" t="s">
+        <v>21</v>
+      </c>
+      <c r="H83" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>1206</v>
+      </c>
+      <c r="C84">
+        <v>87720</v>
+      </c>
+      <c r="D84">
+        <v>24</v>
+      </c>
+      <c r="E84" t="s">
+        <v>54</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" t="s">
+        <v>21</v>
+      </c>
+      <c r="H84" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>1221</v>
+      </c>
+      <c r="C85">
+        <v>88440</v>
+      </c>
+      <c r="D85">
+        <v>24</v>
+      </c>
+      <c r="E85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F85" t="s">
+        <v>41</v>
+      </c>
+      <c r="G85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>1236</v>
+      </c>
+      <c r="C86">
+        <v>89160</v>
+      </c>
+      <c r="D86">
+        <v>24</v>
+      </c>
+      <c r="E86" t="s">
+        <v>54</v>
+      </c>
+      <c r="F86" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>1251</v>
+      </c>
+      <c r="C87">
+        <v>89880</v>
+      </c>
+      <c r="D87">
+        <v>24</v>
+      </c>
+      <c r="E87" t="s">
+        <v>54</v>
+      </c>
+      <c r="F87" t="s">
+        <v>41</v>
+      </c>
+      <c r="G87" t="s">
+        <v>21</v>
+      </c>
+      <c r="H87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>1266</v>
+      </c>
+      <c r="C88">
+        <v>90600</v>
+      </c>
+      <c r="D88">
+        <v>24</v>
+      </c>
+      <c r="E88" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" t="s">
+        <v>41</v>
+      </c>
+      <c r="G88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>1281</v>
+      </c>
+      <c r="C89">
+        <v>91320</v>
+      </c>
+      <c r="D89">
+        <v>24</v>
+      </c>
+      <c r="E89" t="s">
+        <v>54</v>
+      </c>
+      <c r="F89" t="s">
+        <v>41</v>
+      </c>
+      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>1296</v>
+      </c>
+      <c r="C90">
+        <v>92040</v>
+      </c>
+      <c r="D90">
+        <v>24</v>
+      </c>
+      <c r="E90" t="s">
+        <v>54</v>
+      </c>
+      <c r="F90" t="s">
+        <v>41</v>
+      </c>
+      <c r="G90" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>1311</v>
+      </c>
+      <c r="C91">
+        <v>92760</v>
+      </c>
+      <c r="D91">
+        <v>24</v>
+      </c>
+      <c r="E91" t="s">
+        <v>54</v>
+      </c>
+      <c r="F91" t="s">
+        <v>41</v>
+      </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>1326</v>
+      </c>
+      <c r="C92">
+        <v>93480</v>
+      </c>
+      <c r="D92">
+        <v>24</v>
+      </c>
+      <c r="E92" t="s">
+        <v>54</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>21</v>
+      </c>
+      <c r="H92" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>1341</v>
+      </c>
+      <c r="C93">
+        <v>94200</v>
+      </c>
+      <c r="D93">
+        <v>24</v>
+      </c>
+      <c r="E93" t="s">
+        <v>54</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" t="s">
+        <v>21</v>
+      </c>
+      <c r="H93" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>1356</v>
+      </c>
+      <c r="C94">
+        <v>94920</v>
+      </c>
+      <c r="D94">
+        <v>24</v>
+      </c>
+      <c r="E94" t="s">
+        <v>54</v>
+      </c>
+      <c r="F94" t="s">
+        <v>41</v>
+      </c>
+      <c r="G94" t="s">
+        <v>21</v>
+      </c>
+      <c r="H94" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>1371</v>
+      </c>
+      <c r="C95">
+        <v>95640</v>
+      </c>
+      <c r="D95">
+        <v>24</v>
+      </c>
+      <c r="E95" t="s">
+        <v>54</v>
+      </c>
+      <c r="F95" t="s">
+        <v>41</v>
+      </c>
+      <c r="G95" t="s">
+        <v>21</v>
+      </c>
+      <c r="H95" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>1386</v>
+      </c>
+      <c r="C96">
+        <v>96360</v>
+      </c>
+      <c r="D96">
+        <v>24</v>
+      </c>
+      <c r="E96" t="s">
+        <v>54</v>
+      </c>
+      <c r="F96" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" t="s">
+        <v>21</v>
+      </c>
+      <c r="H96" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>1401</v>
+      </c>
+      <c r="C97">
+        <v>97080</v>
+      </c>
+      <c r="D97">
+        <v>24</v>
+      </c>
+      <c r="E97" t="s">
+        <v>54</v>
+      </c>
+      <c r="F97" t="s">
+        <v>41</v>
+      </c>
+      <c r="G97" t="s">
+        <v>21</v>
+      </c>
+      <c r="H97" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>1416</v>
+      </c>
+      <c r="C98">
+        <v>97800</v>
+      </c>
+      <c r="D98">
+        <v>24</v>
+      </c>
+      <c r="E98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" t="s">
+        <v>41</v>
+      </c>
+      <c r="G98" t="s">
+        <v>21</v>
+      </c>
+      <c r="H98" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>1431</v>
+      </c>
+      <c r="C99">
+        <v>98520</v>
+      </c>
+      <c r="D99">
+        <v>24</v>
+      </c>
+      <c r="E99" t="s">
+        <v>54</v>
+      </c>
+      <c r="F99" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" t="s">
+        <v>21</v>
+      </c>
+      <c r="H99" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>1446</v>
+      </c>
+      <c r="C100">
+        <v>99240</v>
+      </c>
+      <c r="D100">
+        <v>24</v>
+      </c>
+      <c r="E100" t="s">
+        <v>54</v>
+      </c>
+      <c r="F100" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" t="s">
+        <v>21</v>
+      </c>
+      <c r="H100" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>1461</v>
+      </c>
+      <c r="C101">
+        <v>99960</v>
+      </c>
+      <c r="D101">
+        <v>24</v>
+      </c>
+      <c r="E101" t="s">
+        <v>54</v>
+      </c>
+      <c r="F101" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" t="s">
+        <v>21</v>
+      </c>
+      <c r="H101" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>1476</v>
+      </c>
+      <c r="C102">
+        <v>100680</v>
+      </c>
+      <c r="D102">
+        <v>24</v>
+      </c>
+      <c r="E102" t="s">
+        <v>54</v>
+      </c>
+      <c r="F102" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" t="s">
+        <v>21</v>
+      </c>
+      <c r="H102" t="s">
         <v>58</v>
       </c>
     </row>
